--- a/docs/ValueSet-ahip-military-service-period.xlsx
+++ b/docs/ValueSet-ahip-military-service-period.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,6 +84,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Used as the answer options for the military service period question in the Military Service Section, capturing which U.S. military service period(s) a patient served in; only shown when the patient indicates they have served.</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -99,67 +102,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>P0911</t>
-  </si>
-  <si>
-    <t>September 2001 or later (Post 9/11)</t>
-  </si>
-  <si>
-    <t>GULFW</t>
-  </si>
-  <si>
-    <t>August 1990 through August 2001 (including the Persian Gulf War)</t>
-  </si>
-  <si>
-    <t>Y7590</t>
-  </si>
-  <si>
-    <t>June 1975 through July 1990</t>
-  </si>
-  <si>
-    <t>VIETN</t>
-  </si>
-  <si>
-    <t>August 1964 through May 1975 (including the Vietnam War)</t>
-  </si>
-  <si>
-    <t>Y5564</t>
-  </si>
-  <si>
-    <t>February 1955 through July 1964</t>
-  </si>
-  <si>
-    <t>KOREA</t>
-  </si>
-  <si>
-    <t>June 1950 through January 1955 (including the Korean War)</t>
-  </si>
-  <si>
-    <t>Y4750</t>
-  </si>
-  <si>
-    <t>January 1947 through May 1950</t>
-  </si>
-  <si>
-    <t>WWII</t>
-  </si>
-  <si>
-    <t>December 1941 through December 1946 (including World War II)</t>
-  </si>
-  <si>
-    <t>PRE41</t>
-  </si>
-  <si>
-    <t>November 1941 or earlier</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-military-period</t>
+    <t>http://terminology.hl7.org/CodeSystem/us-military-service-period</t>
   </si>
 </sst>
 </file>
@@ -393,29 +345,29 @@
         <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -425,7 +377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -434,98 +386,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-military-service-period.xlsx
+++ b/docs/ValueSet-ahip-military-service-period.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html</t>
   </si>
   <si>
     <t>Immutable</t>
